--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484826_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484826_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0447</v>
+        <v>6.2366</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3614</v>
+        <v>4.3945</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6833</v>
+        <v>1.8421</v>
       </c>
       <c r="G2" t="n">
         <v>4.5722</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5314</v>
+        <v>0.6604</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5044</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.027</v>
+        <v>0.1317</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5057</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.079</v>
+        <v>3.283</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5701</v>
+        <v>1.9591</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5089</v>
+        <v>1.3239</v>
       </c>
       <c r="G3" t="n">
-        <v>0.886</v>
+        <v>3.6446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7059</v>
+        <v>1.9126</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1801</v>
+        <v>1.732</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2552</v>
+        <v>2.8657</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9673</v>
+        <v>1.4587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2879</v>
+        <v>1.4069</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3692</v>
+        <v>0.779</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2614</v>
+        <v>0.4539</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1078</v>
+        <v>0.325</v>
       </c>
       <c r="P3" t="n">
         <v>-0.3774</v>
@@ -688,28 +688,28 @@
         <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7363</v>
+        <v>0.6194</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3342</v>
+        <v>0.4901</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4022</v>
+        <v>0.1294</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1659</v>
+        <v>-0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6226</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7885</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4372</v>
+        <v>2.5371</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1927</v>
+        <v>1.0418</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2446</v>
+        <v>1.4952</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6446</v>
+        <v>0.8007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9126</v>
+        <v>0.7466</v>
       </c>
       <c r="I4" t="n">
-        <v>1.732</v>
+        <v>0.0542</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8657</v>
+        <v>1.0341</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4587</v>
+        <v>0.8937</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4069</v>
+        <v>0.1404</v>
       </c>
       <c r="M4" t="n">
-        <v>0.779</v>
+        <v>-0.2334</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4539</v>
+        <v>-0.1471</v>
       </c>
       <c r="O4" t="n">
-        <v>0.325</v>
+        <v>-0.0863</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3774</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.6418</v>
+        <v>-3.0192</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7736</v>
+        <v>0.7517</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7236</v>
+        <v>0.5365</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05</v>
+        <v>0.2152</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6036</v>
+        <v>2.3055</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>2.4904</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8488</v>
+        <v>-0.1849</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5485</v>
+        <v>2.2072</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1061</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4423</v>
+        <v>1.4295</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8007</v>
+        <v>0.886</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7466</v>
+        <v>0.7059</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0542</v>
+        <v>0.1801</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0341</v>
+        <v>1.2552</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8937</v>
+        <v>0.9673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1404</v>
+        <v>0.2879</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2334</v>
+        <v>-0.3692</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1471</v>
+        <v>-0.2614</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0863</v>
+        <v>-0.1078</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3209</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0192</v>
+        <v>-2.6418</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2369</v>
+        <v>1.8645</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3992</v>
+        <v>1.5417</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1623</v>
+        <v>0.3228</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3055</v>
+        <v>-0.1659</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4904</v>
+        <v>0.6226</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1849</v>
+        <v>-0.7885</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUÑOZ</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9339</v>
+        <v>1.2523</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9339</v>
+        <v>1.718</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.4657</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9339</v>
+        <v>2.3533</v>
       </c>
       <c r="H6" t="n">
-        <v>0.317</v>
+        <v>1.8141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.617</v>
+        <v>0.5392</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9339</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.317</v>
+        <v>1.49</v>
       </c>
       <c r="L6" t="n">
-        <v>0.617</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.4717</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.1476</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.2079</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.8051</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3277</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.4774</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.7356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. MARTINEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.9339</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4644</v>
+        <v>0.9339</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5979</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3533</v>
+        <v>0.9339</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8141</v>
+        <v>0.317</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5392</v>
+        <v>0.617</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.9339</v>
       </c>
       <c r="K7" t="n">
-        <v>1.49</v>
+        <v>0.317</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.617</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4717</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1476</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2079</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4191</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3451</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.7356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4086</v>
+        <v>0.3557</v>
       </c>
       <c r="E8" t="n">
         <v>0.1828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2258</v>
+        <v>0.1729</v>
       </c>
       <c r="G8" t="n">
         <v>0.3263</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0823</v>
+        <v>0.0294</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2587</v>
+        <v>0.2058</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4687</v>
+        <v>-0.0609</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5377</v>
+        <v>-0.0506</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="G9" t="n">
         <v>-0.278</v>
@@ -1156,13 +1156,13 @@
         <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1111</v>
+        <v>0.5189</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.458</v>
+        <v>0.0292</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.4897</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3018</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7148</v>
+        <v>-0.9362</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0587</v>
+        <v>1.8639</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7736</v>
+        <v>-2.8</v>
       </c>
       <c r="G10" t="n">
         <v>1.0261</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3721</v>
+        <v>0.1508</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3556</v>
+        <v>0.1608</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4904</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-1.5264</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3786</v>
+        <v>-0.8657</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.502</v>
+        <v>-0.6607</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0575</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6636</v>
+        <v>1.0177</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0175</v>
+        <v>0.5304</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6461</v>
+        <v>0.4874</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4867</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2226</v>
+        <v>-1.9567</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5189</v>
+        <v>0.8112</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7415</v>
+        <v>-2.768</v>
       </c>
       <c r="G12" t="n">
         <v>2.4703</v>
@@ -1390,13 +1390,13 @@
         <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0176</v>
+        <v>0.2482</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.458</v>
+        <v>-0.1657</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4403</v>
+        <v>0.4139</v>
       </c>
       <c r="V12" t="n">
         <v>-3.9205</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.0317</v>
+        <v>12.3256</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4727</v>
+        <v>12.7666</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4411</v>
+        <v>-0.4410999999999992</v>
       </c>
       <c r="G13" t="n">
         <v>14.6779</v>
@@ -1450,7 +1450,7 @@
         <v>8.5495</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.06159999999999999</v>
+        <v>-0.06160000000000021</v>
       </c>
       <c r="N13" t="n">
         <v>-0.8216999999999999</v>
@@ -1468,10 +1468,10 @@
         <v>11.322</v>
       </c>
       <c r="S13" t="n">
-        <v>6.372199999999999</v>
+        <v>6.666099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5089</v>
+        <v>3.802999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2.8633</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6857</v>
+        <v>2.0778</v>
       </c>
       <c r="E14" t="n">
         <v>3.1469</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4612</v>
+        <v>-1.0691</v>
       </c>
       <c r="G14" t="n">
         <v>-1.9618</v>
@@ -1546,13 +1546,13 @@
         <v>2.8305</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5978</v>
+        <v>-1.2057</v>
       </c>
       <c r="T14" t="n">
         <v>-0.5139</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0839</v>
+        <v>-0.6918</v>
       </c>
       <c r="V14" t="n">
         <v>2.7922</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1176</v>
+        <v>1.6721</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4975</v>
+        <v>3.7898</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3799</v>
+        <v>-2.1177</v>
       </c>
       <c r="G15" t="n">
         <v>2.2283</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1863</v>
+        <v>-0.6318</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7519</v>
+        <v>-0.4596</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4344</v>
+        <v>-0.1722</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8931</v>
+        <v>0.1451</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4426</v>
+        <v>3.858</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5495</v>
+        <v>-3.713</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9136</v>
@@ -1702,13 +1702,13 @@
         <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0335</v>
+        <v>-0.7145</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1822</v>
+        <v>-0.4024</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1486</v>
+        <v>-0.3121</v>
       </c>
       <c r="V16" t="n">
         <v>2.7732</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6216</v>
+        <v>-0.5951</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1352</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4864</v>
+        <v>-0.4599</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3329</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2886</v>
+        <v>-0.2622</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9887</v>
+        <v>-2.3056</v>
       </c>
       <c r="E18" t="n">
         <v>-1.1563</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8324</v>
+        <v>-1.1494</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1147</v>
@@ -1858,13 +1858,13 @@
         <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6854</v>
+        <v>-1.0023</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3375</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3479</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.3018</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0089</v>
+        <v>-3.8884</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3107</v>
+        <v>-2.921</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.9674</v>
       </c>
       <c r="G19" t="n">
         <v>-3.8828</v>
@@ -1936,13 +1936,13 @@
         <v>2.4531</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3338</v>
+        <v>-0.2134</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9283</v>
+        <v>-0.5385</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5944</v>
+        <v>0.3252</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9244</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.109</v>
+        <v>-7.8384</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.0437</v>
+        <v>-6.1412</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0653</v>
+        <v>-1.6973</v>
       </c>
       <c r="G20" t="n">
         <v>-5.7004</v>
@@ -2014,13 +2014,13 @@
         <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3139</v>
+        <v>-1.0433</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3375</v>
+        <v>-0.4349</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9764</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>1.547</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-12.0318</v>
+        <v>-10.7325</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4410999999999996</v>
+        <v>0.4410000000000016</v>
       </c>
       <c r="F21" t="n">
-        <v>-12.4728</v>
+        <v>-11.1738</v>
       </c>
       <c r="G21" t="n">
         <v>-14.6779</v>
@@ -2092,13 +2092,13 @@
         <v>14.1525</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.372300000000001</v>
+        <v>-5.0732</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.8633</v>
+        <v>-2.8632</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.5091</v>
+        <v>-2.2099</v>
       </c>
       <c r="V21" t="n">
         <v>6.188</v>
